--- a/py/out.xlsx
+++ b/py/out.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C130"/>
+  <dimension ref="A1:C212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,12 +434,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 52016, 6]</t>
+          <t>['10.80.4.49', '170.72.245.92', 1500, 443, 6]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 52016</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 170.72.245.92 &amp;&amp; tcp.port == 1500 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -449,12 +449,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 44336, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 52016, 6]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 44336</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 52016</t>
         </is>
       </c>
     </row>
@@ -464,12 +464,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 44339, 6]</t>
+          <t>['10.80.4.49', '52.97.232.210', 1491, 443, 6]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 44339</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 52.97.232.210 &amp;&amp; tcp.port == 1491 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -479,12 +479,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 44342, 6]</t>
+          <t>['170.72.17.208', '10.80.4.49', 8934, 35111, 6]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 44342</t>
+          <t>ip.addr == 170.72.17.208 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 8934 &amp;&amp; tcp.port == 35111</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 44345, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 44336, 6]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 44345</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 44336</t>
         </is>
       </c>
     </row>
@@ -509,12 +509,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 1149, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 44339, 6]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 1149</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 44339</t>
         </is>
       </c>
     </row>
@@ -524,12 +524,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 1152, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 44342, 6]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 1152</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 44342</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 1154, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 44345, 6]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 1154</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 44345</t>
         </is>
       </c>
     </row>
@@ -554,12 +554,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 20699, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 1149, 6]</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 20699</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 1149</t>
         </is>
       </c>
     </row>
@@ -569,12 +569,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 49874, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 1152, 6]</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 49874</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 1152</t>
         </is>
       </c>
     </row>
@@ -584,12 +584,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 49878, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 1154, 6]</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 49878</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 1154</t>
         </is>
       </c>
     </row>
@@ -599,12 +599,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 49882, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 20699, 6]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 49882</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 20699</t>
         </is>
       </c>
     </row>
@@ -614,12 +614,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 49885, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 49874, 6]</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 49885</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 49874</t>
         </is>
       </c>
     </row>
@@ -629,12 +629,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 41896, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 49878, 6]</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 41896</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 49878</t>
         </is>
       </c>
     </row>
@@ -644,12 +644,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 41898, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 49882, 6]</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 41898</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 49882</t>
         </is>
       </c>
     </row>
@@ -659,12 +659,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 25530, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 49885, 6]</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 25530</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 49885</t>
         </is>
       </c>
     </row>
@@ -674,12 +674,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 25533, 6]</t>
+          <t>['40.114.177.156', '10.80.4.49', 443, 18979, 6]</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 25533</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 18979</t>
         </is>
       </c>
     </row>
@@ -689,12 +689,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 25537, 6]</t>
+          <t>['151.101.67.42', '10.80.4.49', 443, 45263, 6]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 25537</t>
+          <t>ip.addr == 151.101.67.42 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 45263</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 25540, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 41896, 6]</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 25540</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 41896</t>
         </is>
       </c>
     </row>
@@ -719,12 +719,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 64716, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 41898, 6]</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 64716</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 41898</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 64721, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 25530, 6]</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 64721</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 25530</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 41892, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 25533, 6]</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 41892</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 25533</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 1190, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 25537, 6]</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 1190</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 25537</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 20667, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 25540, 6]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 20667</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 25540</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 20670, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 64716, 6]</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 20670</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 64716</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 20673, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 64721, 6]</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 20673</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 64721</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 20675, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 41892, 6]</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 20675</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 41892</t>
         </is>
       </c>
     </row>
@@ -839,12 +839,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 3046, 6]</t>
+          <t>['40.114.177.156', '10.80.4.49', 443, 41918, 6]</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 3046</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 41918</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 3048, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 1190, 6]</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 3048</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 1190</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 3052, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 20667, 6]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 3052</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 20667</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 50366, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 20670, 6]</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 50366</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 20670</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 41903, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 20673, 6]</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 41903</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 20673</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 27220, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 20675, 6]</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 27220</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 20675</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 27224, 6]</t>
+          <t>['40.114.177.156', '10.80.4.49', 443, 20679, 6]</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 27224</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 20679</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 27226, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 3046, 6]</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 27226</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 3046</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 51131, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 3048, 6]</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 51131</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 3048</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 51134, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 3052, 6]</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 51134</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 3052</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 51136, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 50366, 6]</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 51136</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 50366</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 51139, 6]</t>
+          <t>['40.114.177.156', '10.80.4.49', 443, 50367, 6]</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 51139</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 50367</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 36234, 6]</t>
+          <t>['40.114.177.156', '10.80.4.49', 443, 50373, 6]</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 36234</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 50373</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 36237, 6]</t>
+          <t>['48.222.183.128', '10.80.4.49', 443, 29356, 6]</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 36237</t>
+          <t>ip.addr == 48.222.183.128 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 29356</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 23428, 6]</t>
+          <t>['150.171.110.53', '10.80.4.49', 443, 21050, 6]</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 23428</t>
+          <t>ip.addr == 150.171.110.53 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 21050</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 11828, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 41903, 6]</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 11828</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 41903</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 20232, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 27220, 6]</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 20232</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 27220</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 20236, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 27224, 6]</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 20236</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 27224</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 20239, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 27226, 6]</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 20239</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 27226</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 53797, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 51131, 6]</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 53797</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 51131</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 26276, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 51134, 6]</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 26276</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 51134</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 26278, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 51136, 6]</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 26278</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 51136</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 24451, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 51139, 6]</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 24451</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 51139</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 24453, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 36234, 6]</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 24453</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 36234</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 20377, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 36237, 6]</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 20377</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 36237</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 54081, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 23428, 6]</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54081</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 23428</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 54083, 6]</t>
+          <t>['89.187.165.194', '10.80.4.49', 443, 23245, 6]</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54083</t>
+          <t>ip.addr == 89.187.165.194 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 23245</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 54086, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 11828, 6]</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54086</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 11828</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 3220, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 20232, 6]</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 3220</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 20232</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 3233, 6]</t>
+          <t>['170.72.245.245', '10.80.4.49', 443, 20234, 6]</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 3233</t>
+          <t>ip.addr == 170.72.245.245 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 20234</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 31307, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 20236, 6]</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 31307</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 20236</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 36557, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 20239, 6]</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 36557</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 20239</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 48189, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 53797, 6]</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 48189</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 53797</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 21052, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 26276, 6]</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 21052</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 26276</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 46269, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 26278, 6]</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 46269</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 26278</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 17535, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 24451, 6]</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 17535</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 24451</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 14630, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 24453, 6]</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14630</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 24453</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 14633, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 20377, 6]</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14633</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 20377</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 14636, 6]</t>
+          <t>['150.171.110.53', '10.80.4.49', 443, 23611, 6]</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14636</t>
+          <t>ip.addr == 150.171.110.53 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 23611</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 14639, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 54081, 6]</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14639</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54081</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 14642, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 54083, 6]</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14642</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54083</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 14644, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 54086, 6]</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14644</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54086</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 14649, 6]</t>
+          <t>['140.82.121.6', '10.80.4.49', 443, 3219, 6]</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14649</t>
+          <t>ip.addr == 140.82.121.6 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 3219</t>
         </is>
       </c>
     </row>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 14651, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 3220, 6]</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14651</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 3220</t>
         </is>
       </c>
     </row>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 52041, 6]</t>
+          <t>['40.114.177.156', '10.80.4.49', 443, 3222, 6]</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 52041</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 3222</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 52044, 6]</t>
+          <t>['40.114.177.156', '10.80.4.49', 443, 3226, 6]</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 52044</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 3226</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 52047, 6]</t>
+          <t>['40.114.177.156', '10.80.4.49', 443, 3227, 6]</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 52047</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 3227</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 52050, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 3233, 6]</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 52050</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 3233</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 52052, 6]</t>
+          <t>['48.222.183.128', '10.80.4.49', 443, 63485, 6]</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 52052</t>
+          <t>ip.addr == 48.222.183.128 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 63485</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 52055, 6]</t>
+          <t>['40.114.178.124', '10.80.4.49', 443, 31637, 6]</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 52055</t>
+          <t>ip.addr == 40.114.178.124 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 31637</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 52057, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 31307, 6]</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 52057</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 31307</t>
         </is>
       </c>
     </row>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 36880, 6]</t>
+          <t>['40.114.177.156', '10.80.4.49', 443, 36554, 6]</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 36880</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 36554</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 21312, 6]</t>
+          <t>['40.114.177.156', '10.80.4.49', 443, 36553, 6]</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 21312</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 36553</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 14089, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 36557, 6]</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14089</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 36557</t>
         </is>
       </c>
     </row>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 14260, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 48189, 6]</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14260</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 48189</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 24705, 6]</t>
+          <t>['40.114.177.156', '10.80.4.49', 443, 21051, 6]</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 24705</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 21051</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 19977, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 21052, 6]</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 19977</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 21052</t>
         </is>
       </c>
     </row>
@@ -1694,12 +1694,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 19979, 6]</t>
+          <t>['40.114.177.156', '10.80.4.49', 443, 28504, 6]</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 19979</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 28504</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 19982, 6]</t>
+          <t>['104.18.32.137', '10.80.4.49', 443, 28133, 6]</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 19982</t>
+          <t>ip.addr == 104.18.32.137 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 28133</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1724,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 10318, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 46269, 6]</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 10318</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 46269</t>
         </is>
       </c>
     </row>
@@ -1739,12 +1739,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 10322, 6]</t>
+          <t>['44.233.44.36', '10.80.4.49', 443, 48425, 6]</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 10322</t>
+          <t>ip.addr == 44.233.44.36 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 48425</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 10329, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 17535, 6]</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 10329</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 17535</t>
         </is>
       </c>
     </row>
@@ -1769,12 +1769,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 27205, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 14630, 6]</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 27205</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14630</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 64799, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 14633, 6]</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 64799</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14633</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 61586, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 14636, 6]</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 61586</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14636</t>
         </is>
       </c>
     </row>
@@ -1814,12 +1814,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 41897, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 14639, 6]</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 41897</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14639</t>
         </is>
       </c>
     </row>
@@ -1829,12 +1829,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 33910, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 14642, 6]</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 33910</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14642</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 21584, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 14644, 6]</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 21584</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14644</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 21594, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 14649, 6]</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 21594</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14649</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 21597, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 14651, 6]</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 21597</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14651</t>
         </is>
       </c>
     </row>
@@ -1889,12 +1889,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 21600, 6]</t>
+          <t>['150.171.110.54', '10.80.4.49', 443, 52039, 6]</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 21600</t>
+          <t>ip.addr == 150.171.110.54 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 52039</t>
         </is>
       </c>
     </row>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 21603, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 52041, 6]</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 21603</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 52041</t>
         </is>
       </c>
     </row>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 21607, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 52044, 6]</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 21607</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 52044</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 21609, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 52047, 6]</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 21609</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 52047</t>
         </is>
       </c>
     </row>
@@ -1949,12 +1949,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 60528, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 52050, 6]</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 60528</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 52050</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 60530, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 52052, 6]</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 60530</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 52052</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 60533, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 52055, 6]</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 60533</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 52055</t>
         </is>
       </c>
     </row>
@@ -1994,12 +1994,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 17140, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 52057, 6]</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 17140</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 52057</t>
         </is>
       </c>
     </row>
@@ -2009,12 +2009,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 24751, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 36880, 6]</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 24751</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 36880</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 24754, 6]</t>
+          <t>['170.72.245.245', '10.80.4.49', 443, 36881, 6]</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 24754</t>
+          <t>ip.addr == 170.72.245.245 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 36881</t>
         </is>
       </c>
     </row>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 24757, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 21312, 6]</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 24757</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 21312</t>
         </is>
       </c>
     </row>
@@ -2054,12 +2054,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 9137, 6]</t>
+          <t>['40.114.177.156', '10.80.4.49', 443, 21313, 6]</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 9137</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 21313</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 9139, 6]</t>
+          <t>['40.114.177.156', '10.80.4.49', 443, 21314, 6]</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 9139</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 21314</t>
         </is>
       </c>
     </row>
@@ -2084,12 +2084,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 6364, 6]</t>
+          <t>['40.114.177.156', '10.80.4.49', 443, 21316, 6]</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 6364</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 21316</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 6366, 6]</t>
+          <t>['40.114.177.156', '10.80.4.49', 443, 21317, 6]</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 6366</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 21317</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 6369, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 14089, 6]</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 6369</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14089</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 54857, 6]</t>
+          <t>['193.247.41.17', '10.80.4.49', 443, 1270, 6]</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54857</t>
+          <t>ip.addr == 193.247.41.17 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 1270</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 54868, 6]</t>
+          <t>['172.217.208.97', '10.80.4.49', 443, 14255, 6]</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54868</t>
+          <t>ip.addr == 172.217.208.97 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 14255</t>
         </is>
       </c>
     </row>
@@ -2159,12 +2159,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 54870, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 14260, 6]</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54870</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14260</t>
         </is>
       </c>
     </row>
@@ -2174,12 +2174,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 54874, 6]</t>
+          <t>['88.214.205.144', '10.80.4.49', 443, 30964, 6]</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54874</t>
+          <t>ip.addr == 88.214.205.144 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 30964</t>
         </is>
       </c>
     </row>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 54880, 6]</t>
+          <t>['204.62.13.147', '10.80.4.49', 443, 12102, 6]</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54880</t>
+          <t>ip.addr == 204.62.13.147 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 12102</t>
         </is>
       </c>
     </row>
@@ -2204,12 +2204,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 54883, 6]</t>
+          <t>['37.252.171.84', '10.80.4.49', 443, 43404, 6]</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54883</t>
+          <t>ip.addr == 37.252.171.84 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 43404</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 54886, 6]</t>
+          <t>['10.129.129.9', '10.80.4.49', 443, 47122, 6]</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54886</t>
+          <t>ip.addr == 10.129.129.9 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 47122</t>
         </is>
       </c>
     </row>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 54888, 6]</t>
+          <t>['88.214.205.144', '10.80.4.49', 443, 34710, 6]</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54888</t>
+          <t>ip.addr == 88.214.205.144 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 34710</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 54891, 6]</t>
+          <t>['204.62.13.147', '10.80.4.49', 443, 63482, 6]</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54891</t>
+          <t>ip.addr == 204.62.13.147 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 63482</t>
         </is>
       </c>
     </row>
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 54894, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 24705, 6]</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54894</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 24705</t>
         </is>
       </c>
     </row>
@@ -2279,12 +2279,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 54897, 6]</t>
+          <t>['37.252.171.84', '10.80.4.49', 443, 24720, 6]</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54897</t>
+          <t>ip.addr == 37.252.171.84 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 24720</t>
         </is>
       </c>
     </row>
@@ -2294,12 +2294,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 54899, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 19977, 6]</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54899</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 19977</t>
         </is>
       </c>
     </row>
@@ -2309,12 +2309,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 45008, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 19979, 6]</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 45008</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 19979</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 41895, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 19982, 6]</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 41895</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 19982</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 41899, 6]</t>
+          <t>['40.114.177.156', '10.80.4.49', 443, 17799, 6]</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 41899</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 17799</t>
         </is>
       </c>
     </row>
@@ -2354,12 +2354,1242 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
+          <t>['143.204.55.73', '10.80.4.49', 443, 50960, 6]</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ip.addr == 143.204.55.73 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 50960</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 10318, 6]</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 10318</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 10322, 6]</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 10322</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>['40.114.177.156', '10.80.4.49', 443, 10325, 6]</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 10325</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 10329, 6]</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 10329</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>['40.114.177.156', '10.80.4.49', 443, 10334, 6]</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 10334</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>['40.114.177.156', '10.80.4.49', 443, 10336, 6]</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 10336</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>['48.222.183.128', '10.80.4.49', 443, 20290, 6]</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>ip.addr == 48.222.183.128 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 20290</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>['40.114.177.156', '10.80.4.49', 443, 11552, 6]</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 11552</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>['88.214.205.144', '10.80.4.49', 443, 63353, 6]</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>ip.addr == 88.214.205.144 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 63353</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>['51.89.9.254', '10.80.4.49', 443, 8966, 6]</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>ip.addr == 51.89.9.254 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 8966</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>['204.62.13.147', '10.80.4.49', 443, 27456, 6]</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>ip.addr == 204.62.13.147 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 27456</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>['88.214.205.144', '10.80.4.49', 443, 20510, 6]</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>ip.addr == 88.214.205.144 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 20510</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>['204.62.13.147', '10.80.4.49', 443, 50560, 6]</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ip.addr == 204.62.13.147 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 50560</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>['136.243.254.123', '10.80.4.49', 443, 21737, 6]</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ip.addr == 136.243.254.123 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 21737</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>['136.243.254.123', '10.80.4.49', 443, 10580, 6]</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>ip.addr == 136.243.254.123 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 10580</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>['136.243.254.123', '10.80.4.49', 443, 30411, 6]</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>ip.addr == 136.243.254.123 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 30411</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>['136.243.254.123', '10.80.4.49', 443, 27204, 6]</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>ip.addr == 136.243.254.123 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 27204</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 27205, 6]</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 27205</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>['143.204.55.82', '10.80.4.49', 443, 64409, 6]</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ip.addr == 143.204.55.82 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 64409</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>['150.171.110.54', '10.80.4.49', 443, 64797, 6]</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>ip.addr == 150.171.110.54 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 64797</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 64799, 6]</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 64799</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>['40.114.177.156', '10.80.4.49', 443, 64803, 6]</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 64803</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>['40.114.177.156', '10.80.4.49', 443, 64805, 6]</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 64805</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 61586, 6]</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 61586</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>['40.99.217.34', '10.80.4.49', 443, 3257, 6]</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>ip.addr == 40.99.217.34 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 3257</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 41897, 6]</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 41897</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>['140.82.121.3', '10.80.4.49', 443, 9835, 6]</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>ip.addr == 140.82.121.3 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 9835</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 33910, 6]</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 33910</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>['10.129.129.9', '10.80.4.49', 443, 22794, 6]</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>ip.addr == 10.129.129.9 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 22794</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>['192.0.73.2', '10.80.4.49', 443, 12637, 6]</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>ip.addr == 192.0.73.2 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 12637</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 21584, 6]</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 21584</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 21594, 6]</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 21594</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>161</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 21597, 6]</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 21597</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>162</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 21600, 6]</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 21600</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>163</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 21603, 6]</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 21603</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>164</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 21607, 6]</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 21607</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>165</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 21609, 6]</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 21609</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>166</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 60528, 6]</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 60528</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>167</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 60530, 6]</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 60530</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>168</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 60533, 6]</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 60533</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>169</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>['40.114.177.156', '10.80.4.49', 443, 17136, 6]</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 17136</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>170</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>['40.114.177.156', '10.80.4.49', 443, 17135, 6]</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 17135</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>171</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>['40.114.178.124', '10.80.4.49', 443, 17137, 6]</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>ip.addr == 40.114.178.124 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 17137</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>172</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>['40.114.178.124', '10.80.4.49', 443, 17138, 6]</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>ip.addr == 40.114.178.124 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 17138</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>173</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 17140, 6]</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 17140</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>174</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 24751, 6]</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 24751</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>175</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>['40.114.177.156', '10.80.4.49', 443, 24752, 6]</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 24752</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>176</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 24754, 6]</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 24754</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>177</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 24757, 6]</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 24757</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>178</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>['40.114.177.156', '10.80.4.49', 443, 24758, 6]</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 24758</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>179</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 9137, 6]</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 9137</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>180</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 9139, 6]</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 9139</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>181</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>['40.114.177.156', '10.80.4.49', 443, 6361, 6]</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 6361</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>182</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 6364, 6]</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 6364</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>183</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 6366, 6]</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 6366</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>184</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 6369, 6]</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 6369</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>185</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>['13.107.13.93', '10.80.4.49', 443, 6370, 6]</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>ip.addr == 13.107.13.93 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 6370</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>186</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 54857, 6]</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54857</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>187</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 54868, 6]</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54868</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>188</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 54870, 6]</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54870</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>189</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>['10.80.4.49', '170.72.245.92', 1500, 443, 6]</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 170.72.245.92 &amp;&amp; tcp.port == 1500 &amp;&amp; tcp.port == 443</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>190</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 54874, 6]</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54874</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>191</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>['10.80.4.49', '52.97.232.210', 1491, 443, 6]</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 52.97.232.210 &amp;&amp; tcp.port == 1491 &amp;&amp; tcp.port == 443</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>192</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>['170.72.17.208', '10.80.4.49', 8934, 35111, 6]</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>ip.addr == 170.72.17.208 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 8934 &amp;&amp; tcp.port == 35111</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>193</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 54880, 6]</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54880</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>194</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 54883, 6]</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54883</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>195</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 54886, 6]</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54886</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>196</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 54888, 6]</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54888</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>197</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 54891, 6]</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54891</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>198</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 54894, 6]</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54894</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>199</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 54897, 6]</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54897</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>200</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 54899, 6]</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54899</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>201</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 45008, 6]</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 45008</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>202</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>['40.114.177.156', '10.80.4.49', 443, 45010, 6]</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 45010</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>203</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>['40.114.177.156', '10.80.4.49', 443, 45011, 6]</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 45011</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>204</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>['40.114.177.156', '10.80.4.49', 443, 45012, 6]</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 45012</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>205</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>['40.114.177.156', '10.80.4.49', 443, 45014, 6]</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 45014</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>206</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 41895, 6]</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 41895</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>207</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>['146.190.62.39', '10.80.4.49', 80, 41899, 6]</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 41899</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>208</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
           <t>['146.190.62.39', '10.80.4.49', 80, 41902, 6]</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C210" t="inlineStr">
         <is>
           <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 41902</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>209</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>['150.171.110.54', '10.80.4.49', 443, 33727, 6]</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>ip.addr == 150.171.110.54 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 33727</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>210</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>['52.113.194.132', '10.80.4.49', 443, 63461, 6]</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>ip.addr == 52.113.194.132 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 63461</t>
         </is>
       </c>
     </row>
